--- a/calendar/files/2027-calendar-korea.xlsx
+++ b/calendar/files/2027-calendar-korea.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="005F6B65"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -117,24 +121,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +148,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -509,14 +516,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,7 +563,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1월 1일</t>
+          <t>1월 1일(신정)</t>
         </is>
       </c>
     </row>
@@ -641,7 +648,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3·1절</t>
+          <t>3·1절(삼일절)</t>
         </is>
       </c>
     </row>
@@ -930,7 +937,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>기독탄신일</t>
+          <t>기독탄신일(성탄절)</t>
         </is>
       </c>
     </row>
@@ -951,15 +958,35 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>공휴일 기준: 관공서의 공휴일에 관한 규정(2026년 4월 개정 반영). 선거일·임시공휴일은 확정된 날만. calendar.lumenlab.page</t>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>이름은 규정의 이름이고, 괄호 안은 흔히 쓰는 이름이에요. 달력 시트의 칸에는 흔히 쓰는 이름을 적었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>공휴일 기준: 관공서의 공휴일에 관한 규정(2026년 4월 개정 반영). 선거일·임시공휴일은 확정된 날만 들어 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>일요일 시작 기본판이에요. 주 시작 요일이나 용지를 바꾼 달력은 calendar.lumenlab.page 에서 PDF로 받을 수 있어요.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A30:C30"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -982,221 +1009,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 9월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>1
 음 8.1</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>8
 백로</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>14
 추석 연휴</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>15
 추석
 음 8.15</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>16
 추석 연휴</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>23
 추분</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>30
 음 9.1</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1226,102 +1253,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 10월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>1
 음 9.2</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>3
 개천절</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>4
 대체공휴일</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>8
 한로</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>9
 한글날</t>
@@ -1329,132 +1356,132 @@
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>11
 대체공휴일</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>14
 음 9.15</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>24
 상강</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>29
 음 10.1</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1484,218 +1511,218 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 11월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>1
 음 10.4</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>8
 입동</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>12
 음 10.15</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>22
 소설</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>28
 음 11.1</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1725,184 +1752,184 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 12월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>1
 음 11.4</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>7
 대설</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>12
 음 11.15</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>22
 동지</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>25
 성탄절</t>
@@ -1910,39 +1937,39 @@
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>27
 대체공휴일</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>28
 음 12.1</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1972,232 +1999,232 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 1월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>1
 신정
 음 11.24</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>5
 소한</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>8
 음 12.1</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>20
 대한</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>22
 음 12.15</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2227,79 +2254,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 2월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>1
 음 12.25</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>4
 입춘</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>6
 설 연휴</t>
@@ -2307,134 +2334,134 @@
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>7
 설날
 음 1.1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>8
 설 연휴</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>9
 대체공휴일</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>19
 우수</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>21
 음 1.15</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2464,79 +2491,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 3월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>1
 삼일절
 음 1.23</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>6
 경칩</t>
@@ -2544,143 +2571,143 @@
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>8
 음 2.1</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>21
 춘분</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>22
 음 2.15</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2710,218 +2737,218 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 4월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>1
 음 2.25</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>5
 청명</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>7
 음 3.1</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>20
 곡우</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>21
 음 3.15</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2951,57 +2978,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 5월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>1
 노동절
@@ -3010,176 +3037,176 @@
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>3
 대체공휴일</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>5
 어린이날</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>6
 입하
 음 4.1</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>13
 부처님오신날</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>20
 음 4.15</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>21
 소만</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
     </row>
     <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3209,74 +3236,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 6월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>1
 음 4.27</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>5
 음 5.1</t>
@@ -3284,76 +3311,76 @@
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>6
 현충일
 망종</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>19
 음 5.15</t>
@@ -3361,67 +3388,67 @@
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>21
 하지</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3451,142 +3478,142 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 7월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>1
 음 5.27</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>4
 음 6.1</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>7
 소서</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>17
 제헌절</t>
@@ -3594,77 +3621,77 @@
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>18
 음 6.15</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>19
 대체공휴일</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>23
 대서</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -3698,224 +3725,224 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>2027년 8월</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>1
 음 6.29</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>2
 음 7.1</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>8
 입추</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>15
 광복절</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>16
 대체공휴일
 음 7.15</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>23
 처서</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/calendar/files/2027-calendar-korea.xlsx
+++ b/calendar/files/2027-calendar-korea.xlsx
@@ -961,7 +961,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>이름은 규정의 이름이고, 괄호 안은 흔히 쓰는 이름이에요. 달력 시트의 칸에는 흔히 쓰는 이름을 적었어요.</t>
+          <t>이름은 규정의 이름이고, 괄호 안은 흔히 쓰는 이름이에요. 달력 시트의 칸에는 흔히 쓰는 이름을 적었어요(대체공휴일은 무엇의 대체인지 같이).</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,8 @@
       <c r="B4" s="9" t="inlineStr">
         <is>
           <t>4
-대체공휴일</t>
+대체공휴일
+(개천절)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -1364,7 +1365,8 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>11
-대체공휴일</t>
+대체공휴일
+(한글날)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1945,7 +1947,8 @@
       <c r="B7" s="9" t="inlineStr">
         <is>
           <t>27
-대체공휴일</t>
+대체공휴일
+(성탄절)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2350,7 +2353,8 @@
       <c r="C4" s="9" t="inlineStr">
         <is>
           <t>9
-대체공휴일</t>
+대체공휴일
+(설날)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -3045,7 +3049,8 @@
       <c r="B4" s="9" t="inlineStr">
         <is>
           <t>3
-대체공휴일</t>
+대체공휴일
+(노동절)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -3630,7 +3635,8 @@
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>19
-대체공휴일</t>
+대체공휴일
+(제헌절)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3845,7 +3851,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="66" customHeight="1">
+    <row r="5" ht="74" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>15
@@ -3856,6 +3862,7 @@
         <is>
           <t>16
 대체공휴일
+(광복절)
 음 7.15</t>
         </is>
       </c>
